--- a/LubanConfig/MiniTemplate/Datas/生成数据/#怪物基础数据表_3导.xlsx
+++ b/LubanConfig/MiniTemplate/Datas/生成数据/#怪物基础数据表_3导.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="残酷射手" sheetId="1" state="visible" r:id="rId1"/>
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:T23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19.8" customWidth="1" min="2" max="2"/>
@@ -508,6 +508,11 @@
     <col width="8.800000000000001" customWidth="1" min="13" max="13"/>
     <col width="8.800000000000001" customWidth="1" min="14" max="14"/>
     <col width="8.800000000000001" customWidth="1" min="15" max="15"/>
+    <col width="17.6" customWidth="1" min="16" max="16"/>
+    <col width="19.8" customWidth="1" min="17" max="17"/>
+    <col width="13.2" customWidth="1" min="18" max="18"/>
+    <col width="13.2" customWidth="1" min="19" max="19"/>
+    <col width="13.2" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -586,6 +591,31 @@
           <t>名称</t>
         </is>
       </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>血量成长倍率</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>攻击力成长倍率</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>怪物编号</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>适配地图</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>对塔伤害</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -663,6 +693,31 @@
           <t>string</t>
         </is>
       </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -740,6 +795,31 @@
           <t>名称</t>
         </is>
       </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>血量成长倍率</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>攻击力成长倍率</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>怪物编号</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>适配地图</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>对塔伤害</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="B4" s="4" t="inlineStr">
@@ -792,6 +872,23 @@
           <t>残酷射手</t>
         </is>
       </c>
+      <c r="P4" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R4" s="4" t="n">
+        <v>10021</v>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.雪山: '雪山'&gt;, &lt;地图类型.草原: '草原'&gt;]</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" s="4" t="inlineStr">
@@ -844,6 +941,23 @@
           <t>残酷射手</t>
         </is>
       </c>
+      <c r="P5" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>10021</v>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.雪山: '雪山'&gt;, &lt;地图类型.草原: '草原'&gt;]</t>
+        </is>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
@@ -896,6 +1010,23 @@
           <t>残酷射手</t>
         </is>
       </c>
+      <c r="P6" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>10021</v>
+      </c>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.雪山: '雪山'&gt;, &lt;地图类型.草原: '草原'&gt;]</t>
+        </is>
+      </c>
+      <c r="T6" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
@@ -948,6 +1079,23 @@
           <t>残酷射手</t>
         </is>
       </c>
+      <c r="P7" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R7" s="4" t="n">
+        <v>10021</v>
+      </c>
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.雪山: '雪山'&gt;, &lt;地图类型.草原: '草原'&gt;]</t>
+        </is>
+      </c>
+      <c r="T7" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" s="4" t="inlineStr">
@@ -1000,6 +1148,23 @@
           <t>残酷射手</t>
         </is>
       </c>
+      <c r="P8" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>10021</v>
+      </c>
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.雪山: '雪山'&gt;, &lt;地图类型.草原: '草原'&gt;]</t>
+        </is>
+      </c>
+      <c r="T8" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="4" t="inlineStr">
@@ -1052,6 +1217,23 @@
           <t>残酷射手</t>
         </is>
       </c>
+      <c r="P9" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q9" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R9" s="4" t="n">
+        <v>10021</v>
+      </c>
+      <c r="S9" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.雪山: '雪山'&gt;, &lt;地图类型.草原: '草原'&gt;]</t>
+        </is>
+      </c>
+      <c r="T9" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="4" t="inlineStr">
@@ -1104,6 +1286,23 @@
           <t>残酷射手</t>
         </is>
       </c>
+      <c r="P10" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q10" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R10" s="4" t="n">
+        <v>10021</v>
+      </c>
+      <c r="S10" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.雪山: '雪山'&gt;, &lt;地图类型.草原: '草原'&gt;]</t>
+        </is>
+      </c>
+      <c r="T10" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="4" t="inlineStr">
@@ -1156,6 +1355,23 @@
           <t>残酷射手</t>
         </is>
       </c>
+      <c r="P11" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q11" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R11" s="4" t="n">
+        <v>10021</v>
+      </c>
+      <c r="S11" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.雪山: '雪山'&gt;, &lt;地图类型.草原: '草原'&gt;]</t>
+        </is>
+      </c>
+      <c r="T11" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="4" t="inlineStr">
@@ -1208,6 +1424,23 @@
           <t>残酷射手</t>
         </is>
       </c>
+      <c r="P12" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q12" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R12" s="4" t="n">
+        <v>10021</v>
+      </c>
+      <c r="S12" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.雪山: '雪山'&gt;, &lt;地图类型.草原: '草原'&gt;]</t>
+        </is>
+      </c>
+      <c r="T12" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="4" t="inlineStr">
@@ -1260,6 +1493,23 @@
           <t>残酷射手</t>
         </is>
       </c>
+      <c r="P13" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q13" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R13" s="4" t="n">
+        <v>10021</v>
+      </c>
+      <c r="S13" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.雪山: '雪山'&gt;, &lt;地图类型.草原: '草原'&gt;]</t>
+        </is>
+      </c>
+      <c r="T13" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="B14" s="4" t="inlineStr">
@@ -1312,6 +1562,23 @@
           <t>残酷射手</t>
         </is>
       </c>
+      <c r="P14" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q14" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R14" s="4" t="n">
+        <v>10021</v>
+      </c>
+      <c r="S14" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.雪山: '雪山'&gt;, &lt;地图类型.草原: '草原'&gt;]</t>
+        </is>
+      </c>
+      <c r="T14" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="B15" s="4" t="inlineStr">
@@ -1364,6 +1631,23 @@
           <t>残酷射手</t>
         </is>
       </c>
+      <c r="P15" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q15" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R15" s="4" t="n">
+        <v>10021</v>
+      </c>
+      <c r="S15" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.雪山: '雪山'&gt;, &lt;地图类型.草原: '草原'&gt;]</t>
+        </is>
+      </c>
+      <c r="T15" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="B16" s="4" t="inlineStr">
@@ -1416,6 +1700,23 @@
           <t>残酷射手</t>
         </is>
       </c>
+      <c r="P16" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q16" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R16" s="4" t="n">
+        <v>10021</v>
+      </c>
+      <c r="S16" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.雪山: '雪山'&gt;, &lt;地图类型.草原: '草原'&gt;]</t>
+        </is>
+      </c>
+      <c r="T16" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="B17" s="4" t="inlineStr">
@@ -1468,6 +1769,23 @@
           <t>残酷射手</t>
         </is>
       </c>
+      <c r="P17" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q17" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R17" s="4" t="n">
+        <v>10021</v>
+      </c>
+      <c r="S17" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.雪山: '雪山'&gt;, &lt;地图类型.草原: '草原'&gt;]</t>
+        </is>
+      </c>
+      <c r="T17" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="B18" s="4" t="inlineStr">
@@ -1520,6 +1838,23 @@
           <t>残酷射手</t>
         </is>
       </c>
+      <c r="P18" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q18" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R18" s="4" t="n">
+        <v>10021</v>
+      </c>
+      <c r="S18" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.雪山: '雪山'&gt;, &lt;地图类型.草原: '草原'&gt;]</t>
+        </is>
+      </c>
+      <c r="T18" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="B19" s="4" t="inlineStr">
@@ -1572,6 +1907,23 @@
           <t>残酷射手</t>
         </is>
       </c>
+      <c r="P19" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q19" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R19" s="4" t="n">
+        <v>10021</v>
+      </c>
+      <c r="S19" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.雪山: '雪山'&gt;, &lt;地图类型.草原: '草原'&gt;]</t>
+        </is>
+      </c>
+      <c r="T19" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="B20" s="4" t="inlineStr">
@@ -1624,6 +1976,23 @@
           <t>残酷射手</t>
         </is>
       </c>
+      <c r="P20" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q20" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R20" s="4" t="n">
+        <v>10021</v>
+      </c>
+      <c r="S20" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.雪山: '雪山'&gt;, &lt;地图类型.草原: '草原'&gt;]</t>
+        </is>
+      </c>
+      <c r="T20" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="B21" s="4" t="inlineStr">
@@ -1676,6 +2045,23 @@
           <t>残酷射手</t>
         </is>
       </c>
+      <c r="P21" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q21" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R21" s="4" t="n">
+        <v>10021</v>
+      </c>
+      <c r="S21" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.雪山: '雪山'&gt;, &lt;地图类型.草原: '草原'&gt;]</t>
+        </is>
+      </c>
+      <c r="T21" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="B22" s="4" t="inlineStr">
@@ -1728,6 +2114,23 @@
           <t>残酷射手</t>
         </is>
       </c>
+      <c r="P22" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q22" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R22" s="4" t="n">
+        <v>10021</v>
+      </c>
+      <c r="S22" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.雪山: '雪山'&gt;, &lt;地图类型.草原: '草原'&gt;]</t>
+        </is>
+      </c>
+      <c r="T22" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="B23" s="4" t="inlineStr">
@@ -1779,6 +2182,23 @@
         <is>
           <t>残酷射手</t>
         </is>
+      </c>
+      <c r="P23" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q23" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R23" s="4" t="n">
+        <v>10021</v>
+      </c>
+      <c r="S23" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.雪山: '雪山'&gt;, &lt;地图类型.草原: '草原'&gt;]</t>
+        </is>
+      </c>
+      <c r="T23" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1792,7 +2212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:T23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.6" customWidth="1" min="2" max="2"/>
@@ -1809,6 +2229,11 @@
     <col width="8.800000000000001" customWidth="1" min="13" max="13"/>
     <col width="8.800000000000001" customWidth="1" min="14" max="14"/>
     <col width="8.800000000000001" customWidth="1" min="15" max="15"/>
+    <col width="17.6" customWidth="1" min="16" max="16"/>
+    <col width="19.8" customWidth="1" min="17" max="17"/>
+    <col width="13.2" customWidth="1" min="18" max="18"/>
+    <col width="13.2" customWidth="1" min="19" max="19"/>
+    <col width="13.2" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1887,6 +2312,31 @@
           <t>名称</t>
         </is>
       </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>血量成长倍率</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>攻击力成长倍率</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>怪物编号</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>适配地图</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>对塔伤害</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -1964,6 +2414,31 @@
           <t>string</t>
         </is>
       </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -2041,6 +2516,31 @@
           <t>名称</t>
         </is>
       </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>血量成长倍率</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>攻击力成长倍率</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>怪物编号</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>适配地图</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>对塔伤害</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="B4" s="4" t="inlineStr">
@@ -2093,6 +2593,23 @@
           <t>泰森</t>
         </is>
       </c>
+      <c r="P4" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R4" s="4" t="n">
+        <v>10031</v>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" s="4" t="inlineStr">
@@ -2145,6 +2662,23 @@
           <t>泰森</t>
         </is>
       </c>
+      <c r="P5" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>10031</v>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
@@ -2197,6 +2731,23 @@
           <t>泰森</t>
         </is>
       </c>
+      <c r="P6" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>10031</v>
+      </c>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T6" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
@@ -2249,6 +2800,23 @@
           <t>泰森</t>
         </is>
       </c>
+      <c r="P7" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R7" s="4" t="n">
+        <v>10031</v>
+      </c>
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T7" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" s="4" t="inlineStr">
@@ -2301,6 +2869,23 @@
           <t>泰森</t>
         </is>
       </c>
+      <c r="P8" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>10031</v>
+      </c>
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T8" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="4" t="inlineStr">
@@ -2353,6 +2938,23 @@
           <t>泰森</t>
         </is>
       </c>
+      <c r="P9" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q9" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R9" s="4" t="n">
+        <v>10031</v>
+      </c>
+      <c r="S9" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T9" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="4" t="inlineStr">
@@ -2405,6 +3007,23 @@
           <t>泰森</t>
         </is>
       </c>
+      <c r="P10" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q10" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R10" s="4" t="n">
+        <v>10031</v>
+      </c>
+      <c r="S10" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T10" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="4" t="inlineStr">
@@ -2457,6 +3076,23 @@
           <t>泰森</t>
         </is>
       </c>
+      <c r="P11" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q11" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R11" s="4" t="n">
+        <v>10031</v>
+      </c>
+      <c r="S11" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T11" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="4" t="inlineStr">
@@ -2509,6 +3145,23 @@
           <t>泰森</t>
         </is>
       </c>
+      <c r="P12" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q12" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R12" s="4" t="n">
+        <v>10031</v>
+      </c>
+      <c r="S12" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T12" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="4" t="inlineStr">
@@ -2561,6 +3214,23 @@
           <t>泰森</t>
         </is>
       </c>
+      <c r="P13" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q13" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R13" s="4" t="n">
+        <v>10031</v>
+      </c>
+      <c r="S13" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T13" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="B14" s="4" t="inlineStr">
@@ -2613,6 +3283,23 @@
           <t>泰森</t>
         </is>
       </c>
+      <c r="P14" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q14" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R14" s="4" t="n">
+        <v>10031</v>
+      </c>
+      <c r="S14" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T14" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="B15" s="4" t="inlineStr">
@@ -2665,6 +3352,23 @@
           <t>泰森</t>
         </is>
       </c>
+      <c r="P15" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q15" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R15" s="4" t="n">
+        <v>10031</v>
+      </c>
+      <c r="S15" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T15" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="B16" s="4" t="inlineStr">
@@ -2717,6 +3421,23 @@
           <t>泰森</t>
         </is>
       </c>
+      <c r="P16" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q16" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R16" s="4" t="n">
+        <v>10031</v>
+      </c>
+      <c r="S16" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T16" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="B17" s="4" t="inlineStr">
@@ -2769,6 +3490,23 @@
           <t>泰森</t>
         </is>
       </c>
+      <c r="P17" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q17" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R17" s="4" t="n">
+        <v>10031</v>
+      </c>
+      <c r="S17" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T17" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="B18" s="4" t="inlineStr">
@@ -2821,6 +3559,23 @@
           <t>泰森</t>
         </is>
       </c>
+      <c r="P18" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q18" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R18" s="4" t="n">
+        <v>10031</v>
+      </c>
+      <c r="S18" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T18" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="B19" s="4" t="inlineStr">
@@ -2873,6 +3628,23 @@
           <t>泰森</t>
         </is>
       </c>
+      <c r="P19" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q19" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R19" s="4" t="n">
+        <v>10031</v>
+      </c>
+      <c r="S19" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T19" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="B20" s="4" t="inlineStr">
@@ -2925,6 +3697,23 @@
           <t>泰森</t>
         </is>
       </c>
+      <c r="P20" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q20" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R20" s="4" t="n">
+        <v>10031</v>
+      </c>
+      <c r="S20" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T20" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="B21" s="4" t="inlineStr">
@@ -2977,6 +3766,23 @@
           <t>泰森</t>
         </is>
       </c>
+      <c r="P21" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q21" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R21" s="4" t="n">
+        <v>10031</v>
+      </c>
+      <c r="S21" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T21" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="B22" s="4" t="inlineStr">
@@ -3029,6 +3835,23 @@
           <t>泰森</t>
         </is>
       </c>
+      <c r="P22" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q22" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R22" s="4" t="n">
+        <v>10031</v>
+      </c>
+      <c r="S22" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T22" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="B23" s="4" t="inlineStr">
@@ -3080,6 +3903,23 @@
         <is>
           <t>泰森</t>
         </is>
+      </c>
+      <c r="P23" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q23" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R23" s="4" t="n">
+        <v>10031</v>
+      </c>
+      <c r="S23" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T23" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3093,7 +3933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:T23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26.4" customWidth="1" min="2" max="2"/>
@@ -3110,6 +3950,11 @@
     <col width="8.800000000000001" customWidth="1" min="13" max="13"/>
     <col width="8.800000000000001" customWidth="1" min="14" max="14"/>
     <col width="8.800000000000001" customWidth="1" min="15" max="15"/>
+    <col width="17.6" customWidth="1" min="16" max="16"/>
+    <col width="19.8" customWidth="1" min="17" max="17"/>
+    <col width="13.2" customWidth="1" min="18" max="18"/>
+    <col width="13.2" customWidth="1" min="19" max="19"/>
+    <col width="13.2" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3188,6 +4033,31 @@
           <t>名称</t>
         </is>
       </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>血量成长倍率</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>攻击力成长倍率</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>怪物编号</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>适配地图</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>对塔伤害</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -3265,6 +4135,31 @@
           <t>string</t>
         </is>
       </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -3342,6 +4237,31 @@
           <t>名称</t>
         </is>
       </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>血量成长倍率</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>攻击力成长倍率</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>怪物编号</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>适配地图</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>对塔伤害</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="B4" s="4" t="inlineStr">
@@ -3394,6 +4314,23 @@
           <t>萨哈比精英坦克</t>
         </is>
       </c>
+      <c r="P4" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R4" s="4" t="n">
+        <v>20001</v>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.雪山: '雪山'&gt;]</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" s="4" t="inlineStr">
@@ -3446,6 +4383,23 @@
           <t>萨哈比精英坦克</t>
         </is>
       </c>
+      <c r="P5" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>20001</v>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.雪山: '雪山'&gt;]</t>
+        </is>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
@@ -3498,6 +4452,23 @@
           <t>萨哈比精英坦克</t>
         </is>
       </c>
+      <c r="P6" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>20001</v>
+      </c>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.雪山: '雪山'&gt;]</t>
+        </is>
+      </c>
+      <c r="T6" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
@@ -3550,6 +4521,23 @@
           <t>萨哈比精英坦克</t>
         </is>
       </c>
+      <c r="P7" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R7" s="4" t="n">
+        <v>20001</v>
+      </c>
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.雪山: '雪山'&gt;]</t>
+        </is>
+      </c>
+      <c r="T7" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" s="4" t="inlineStr">
@@ -3602,6 +4590,23 @@
           <t>萨哈比精英坦克</t>
         </is>
       </c>
+      <c r="P8" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>20001</v>
+      </c>
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.雪山: '雪山'&gt;]</t>
+        </is>
+      </c>
+      <c r="T8" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="4" t="inlineStr">
@@ -3654,6 +4659,23 @@
           <t>萨哈比精英坦克</t>
         </is>
       </c>
+      <c r="P9" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q9" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R9" s="4" t="n">
+        <v>20001</v>
+      </c>
+      <c r="S9" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.雪山: '雪山'&gt;]</t>
+        </is>
+      </c>
+      <c r="T9" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="4" t="inlineStr">
@@ -3706,6 +4728,23 @@
           <t>萨哈比精英坦克</t>
         </is>
       </c>
+      <c r="P10" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q10" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R10" s="4" t="n">
+        <v>20001</v>
+      </c>
+      <c r="S10" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.雪山: '雪山'&gt;]</t>
+        </is>
+      </c>
+      <c r="T10" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="4" t="inlineStr">
@@ -3758,6 +4797,23 @@
           <t>萨哈比精英坦克</t>
         </is>
       </c>
+      <c r="P11" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q11" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R11" s="4" t="n">
+        <v>20001</v>
+      </c>
+      <c r="S11" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.雪山: '雪山'&gt;]</t>
+        </is>
+      </c>
+      <c r="T11" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="4" t="inlineStr">
@@ -3810,6 +4866,23 @@
           <t>萨哈比精英坦克</t>
         </is>
       </c>
+      <c r="P12" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q12" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R12" s="4" t="n">
+        <v>20001</v>
+      </c>
+      <c r="S12" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.雪山: '雪山'&gt;]</t>
+        </is>
+      </c>
+      <c r="T12" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="4" t="inlineStr">
@@ -3862,6 +4935,23 @@
           <t>萨哈比精英坦克</t>
         </is>
       </c>
+      <c r="P13" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q13" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R13" s="4" t="n">
+        <v>20001</v>
+      </c>
+      <c r="S13" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.雪山: '雪山'&gt;]</t>
+        </is>
+      </c>
+      <c r="T13" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="B14" s="4" t="inlineStr">
@@ -3914,6 +5004,23 @@
           <t>萨哈比精英坦克</t>
         </is>
       </c>
+      <c r="P14" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q14" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R14" s="4" t="n">
+        <v>20001</v>
+      </c>
+      <c r="S14" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.雪山: '雪山'&gt;]</t>
+        </is>
+      </c>
+      <c r="T14" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="15">
       <c r="B15" s="4" t="inlineStr">
@@ -3966,6 +5073,23 @@
           <t>萨哈比精英坦克</t>
         </is>
       </c>
+      <c r="P15" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q15" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R15" s="4" t="n">
+        <v>20001</v>
+      </c>
+      <c r="S15" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.雪山: '雪山'&gt;]</t>
+        </is>
+      </c>
+      <c r="T15" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="16">
       <c r="B16" s="4" t="inlineStr">
@@ -4018,6 +5142,23 @@
           <t>萨哈比精英坦克</t>
         </is>
       </c>
+      <c r="P16" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q16" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R16" s="4" t="n">
+        <v>20001</v>
+      </c>
+      <c r="S16" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.雪山: '雪山'&gt;]</t>
+        </is>
+      </c>
+      <c r="T16" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="17">
       <c r="B17" s="4" t="inlineStr">
@@ -4070,6 +5211,23 @@
           <t>萨哈比精英坦克</t>
         </is>
       </c>
+      <c r="P17" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q17" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R17" s="4" t="n">
+        <v>20001</v>
+      </c>
+      <c r="S17" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.雪山: '雪山'&gt;]</t>
+        </is>
+      </c>
+      <c r="T17" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="B18" s="4" t="inlineStr">
@@ -4122,6 +5280,23 @@
           <t>萨哈比精英坦克</t>
         </is>
       </c>
+      <c r="P18" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q18" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R18" s="4" t="n">
+        <v>20001</v>
+      </c>
+      <c r="S18" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.雪山: '雪山'&gt;]</t>
+        </is>
+      </c>
+      <c r="T18" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="19">
       <c r="B19" s="4" t="inlineStr">
@@ -4174,6 +5349,23 @@
           <t>萨哈比精英坦克</t>
         </is>
       </c>
+      <c r="P19" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q19" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R19" s="4" t="n">
+        <v>20001</v>
+      </c>
+      <c r="S19" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.雪山: '雪山'&gt;]</t>
+        </is>
+      </c>
+      <c r="T19" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="20">
       <c r="B20" s="4" t="inlineStr">
@@ -4226,6 +5418,23 @@
           <t>萨哈比精英坦克</t>
         </is>
       </c>
+      <c r="P20" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q20" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R20" s="4" t="n">
+        <v>20001</v>
+      </c>
+      <c r="S20" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.雪山: '雪山'&gt;]</t>
+        </is>
+      </c>
+      <c r="T20" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="21">
       <c r="B21" s="4" t="inlineStr">
@@ -4278,6 +5487,23 @@
           <t>萨哈比精英坦克</t>
         </is>
       </c>
+      <c r="P21" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q21" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R21" s="4" t="n">
+        <v>20001</v>
+      </c>
+      <c r="S21" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.雪山: '雪山'&gt;]</t>
+        </is>
+      </c>
+      <c r="T21" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="22">
       <c r="B22" s="4" t="inlineStr">
@@ -4330,6 +5556,23 @@
           <t>萨哈比精英坦克</t>
         </is>
       </c>
+      <c r="P22" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q22" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R22" s="4" t="n">
+        <v>20001</v>
+      </c>
+      <c r="S22" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.雪山: '雪山'&gt;]</t>
+        </is>
+      </c>
+      <c r="T22" s="4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="23">
       <c r="B23" s="4" t="inlineStr">
@@ -4381,6 +5624,23 @@
         <is>
           <t>萨哈比精英坦克</t>
         </is>
+      </c>
+      <c r="P23" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q23" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R23" s="4" t="n">
+        <v>20001</v>
+      </c>
+      <c r="S23" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.火山: '火山'&gt;, &lt;地图类型.雪山: '雪山'&gt;]</t>
+        </is>
+      </c>
+      <c r="T23" s="4" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -4394,7 +5654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:T23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19.8" customWidth="1" min="2" max="2"/>
@@ -4411,6 +5671,11 @@
     <col width="8.800000000000001" customWidth="1" min="13" max="13"/>
     <col width="8.800000000000001" customWidth="1" min="14" max="14"/>
     <col width="8.800000000000001" customWidth="1" min="15" max="15"/>
+    <col width="17.6" customWidth="1" min="16" max="16"/>
+    <col width="19.8" customWidth="1" min="17" max="17"/>
+    <col width="13.2" customWidth="1" min="18" max="18"/>
+    <col width="13.2" customWidth="1" min="19" max="19"/>
+    <col width="13.2" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4489,6 +5754,31 @@
           <t>名称</t>
         </is>
       </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>血量成长倍率</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>攻击力成长倍率</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>怪物编号</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>适配地图</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>对塔伤害</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -4566,6 +5856,31 @@
           <t>string</t>
         </is>
       </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -4643,6 +5958,31 @@
           <t>名称</t>
         </is>
       </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>血量成长倍率</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>攻击力成长倍率</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>怪物编号</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>适配地图</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>对塔伤害</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="B4" s="4" t="inlineStr">
@@ -4695,6 +6035,23 @@
           <t>普通坦克</t>
         </is>
       </c>
+      <c r="P4" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R4" s="4" t="n">
+        <v>10011</v>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.草原: '草原'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" s="4" t="inlineStr">
@@ -4747,6 +6104,23 @@
           <t>普通坦克</t>
         </is>
       </c>
+      <c r="P5" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>10011</v>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.草原: '草原'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
@@ -4799,6 +6173,23 @@
           <t>普通坦克</t>
         </is>
       </c>
+      <c r="P6" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>10011</v>
+      </c>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.草原: '草原'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T6" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
@@ -4851,6 +6242,23 @@
           <t>普通坦克</t>
         </is>
       </c>
+      <c r="P7" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R7" s="4" t="n">
+        <v>10011</v>
+      </c>
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.草原: '草原'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T7" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" s="4" t="inlineStr">
@@ -4903,6 +6311,23 @@
           <t>普通坦克</t>
         </is>
       </c>
+      <c r="P8" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q8" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>10011</v>
+      </c>
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.草原: '草原'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T8" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="4" t="inlineStr">
@@ -4955,6 +6380,23 @@
           <t>普通坦克</t>
         </is>
       </c>
+      <c r="P9" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q9" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R9" s="4" t="n">
+        <v>10011</v>
+      </c>
+      <c r="S9" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.草原: '草原'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T9" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="4" t="inlineStr">
@@ -5007,6 +6449,23 @@
           <t>普通坦克</t>
         </is>
       </c>
+      <c r="P10" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q10" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R10" s="4" t="n">
+        <v>10011</v>
+      </c>
+      <c r="S10" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.草原: '草原'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T10" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="4" t="inlineStr">
@@ -5059,6 +6518,23 @@
           <t>普通坦克</t>
         </is>
       </c>
+      <c r="P11" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q11" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R11" s="4" t="n">
+        <v>10011</v>
+      </c>
+      <c r="S11" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.草原: '草原'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T11" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="4" t="inlineStr">
@@ -5111,6 +6587,23 @@
           <t>普通坦克</t>
         </is>
       </c>
+      <c r="P12" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q12" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R12" s="4" t="n">
+        <v>10011</v>
+      </c>
+      <c r="S12" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.草原: '草原'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T12" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="4" t="inlineStr">
@@ -5163,6 +6656,23 @@
           <t>普通坦克</t>
         </is>
       </c>
+      <c r="P13" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q13" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R13" s="4" t="n">
+        <v>10011</v>
+      </c>
+      <c r="S13" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.草原: '草原'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T13" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="14">
       <c r="B14" s="4" t="inlineStr">
@@ -5215,6 +6725,23 @@
           <t>普通坦克</t>
         </is>
       </c>
+      <c r="P14" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q14" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R14" s="4" t="n">
+        <v>10011</v>
+      </c>
+      <c r="S14" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.草原: '草原'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T14" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="15">
       <c r="B15" s="4" t="inlineStr">
@@ -5267,6 +6794,23 @@
           <t>普通坦克</t>
         </is>
       </c>
+      <c r="P15" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q15" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R15" s="4" t="n">
+        <v>10011</v>
+      </c>
+      <c r="S15" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.草原: '草原'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T15" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="B16" s="4" t="inlineStr">
@@ -5319,6 +6863,23 @@
           <t>普通坦克</t>
         </is>
       </c>
+      <c r="P16" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q16" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R16" s="4" t="n">
+        <v>10011</v>
+      </c>
+      <c r="S16" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.草原: '草原'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T16" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="17">
       <c r="B17" s="4" t="inlineStr">
@@ -5371,6 +6932,23 @@
           <t>普通坦克</t>
         </is>
       </c>
+      <c r="P17" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q17" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R17" s="4" t="n">
+        <v>10011</v>
+      </c>
+      <c r="S17" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.草原: '草原'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T17" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="18">
       <c r="B18" s="4" t="inlineStr">
@@ -5423,6 +7001,23 @@
           <t>普通坦克</t>
         </is>
       </c>
+      <c r="P18" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q18" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R18" s="4" t="n">
+        <v>10011</v>
+      </c>
+      <c r="S18" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.草原: '草原'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T18" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
       <c r="B19" s="4" t="inlineStr">
@@ -5475,6 +7070,23 @@
           <t>普通坦克</t>
         </is>
       </c>
+      <c r="P19" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q19" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R19" s="4" t="n">
+        <v>10011</v>
+      </c>
+      <c r="S19" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.草原: '草原'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T19" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="20">
       <c r="B20" s="4" t="inlineStr">
@@ -5527,6 +7139,23 @@
           <t>普通坦克</t>
         </is>
       </c>
+      <c r="P20" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q20" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R20" s="4" t="n">
+        <v>10011</v>
+      </c>
+      <c r="S20" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.草原: '草原'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T20" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
       <c r="B21" s="4" t="inlineStr">
@@ -5579,6 +7208,23 @@
           <t>普通坦克</t>
         </is>
       </c>
+      <c r="P21" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q21" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R21" s="4" t="n">
+        <v>10011</v>
+      </c>
+      <c r="S21" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.草原: '草原'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T21" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="22">
       <c r="B22" s="4" t="inlineStr">
@@ -5631,6 +7277,23 @@
           <t>普通坦克</t>
         </is>
       </c>
+      <c r="P22" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q22" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R22" s="4" t="n">
+        <v>10011</v>
+      </c>
+      <c r="S22" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.草原: '草原'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T22" s="4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="23">
       <c r="B23" s="4" t="inlineStr">
@@ -5682,6 +7345,23 @@
         <is>
           <t>普通坦克</t>
         </is>
+      </c>
+      <c r="P23" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q23" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R23" s="4" t="n">
+        <v>10011</v>
+      </c>
+      <c r="S23" s="4" t="inlineStr">
+        <is>
+          <t>[&lt;地图类型.草原: '草原'&gt;, &lt;地图类型.森林: '森林'&gt;]</t>
+        </is>
+      </c>
+      <c r="T23" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
